--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484181_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484181_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3604</v>
+        <v>4.8234</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5207</v>
+        <v>2.4607</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8397</v>
+        <v>2.3628</v>
       </c>
       <c r="G2" t="n">
         <v>1.4111</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0286</v>
+        <v>0.4917</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2982</v>
+        <v>0.2382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7304</v>
+        <v>0.2535</v>
       </c>
       <c r="V2" t="n">
         <v>1.1352</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.54</v>
+        <v>3.8496</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4071</v>
+        <v>0.3694</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9471</v>
+        <v>3.4802</v>
       </c>
       <c r="G3" t="n">
         <v>3.0507</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9912</v>
+        <v>-0.6816</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4849</v>
+        <v>-0.7084</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5063</v>
+        <v>0.0268</v>
       </c>
       <c r="V3" t="n">
         <v>2.0757</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1759</v>
+        <v>2.4729</v>
       </c>
       <c r="E4" t="n">
-        <v>0.842</v>
+        <v>0.8023</v>
       </c>
       <c r="F4" t="n">
-        <v>1.334</v>
+        <v>1.6706</v>
       </c>
       <c r="G4" t="n">
         <v>3.9401</v>
@@ -766,13 +766,13 @@
         <v>2.7774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8354</v>
+        <v>-0.5384</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1248</v>
+        <v>0.0852</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9603</v>
+        <v>-0.6236</v>
       </c>
       <c r="V4" t="n">
         <v>-0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.494</v>
+        <v>0.5782</v>
       </c>
       <c r="E5" t="n">
         <v>0.0347</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4594</v>
+        <v>0.5435</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0487</v>
@@ -844,13 +844,13 @@
         <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V5" t="n">
         <v>1.2065</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2186</v>
+        <v>0.0616</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.3318</v>
+        <v>-3.7593</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5503</v>
+        <v>3.8209</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6153</v>
@@ -922,13 +922,13 @@
         <v>3.7693</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0273</v>
+        <v>-0.1843</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0541</v>
+        <v>-0.4816</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0268</v>
+        <v>0.2974</v>
       </c>
       <c r="V6" t="n">
         <v>0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8646</v>
+        <v>-0.63</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3702</v>
+        <v>-1.4723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5057</v>
+        <v>0.8423</v>
       </c>
       <c r="G7" t="n">
         <v>0.9733000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.7774</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2266</v>
+        <v>-0.992</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6291</v>
+        <v>-0.7311</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5975</v>
+        <v>-0.2609</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1459</v>
+        <v>-1.0617</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8069</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.339</v>
+        <v>-0.2548</v>
       </c>
       <c r="G8" t="n">
         <v>-1.015</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1309</v>
+        <v>-0.0468</v>
       </c>
       <c r="T8" t="n">
         <v>-0.187</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4418</v>
+        <v>-1.3973</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2704</v>
+        <v>-1.3101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1713</v>
+        <v>-0.0872</v>
       </c>
       <c r="G9" t="n">
         <v>0.5304</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0278</v>
+        <v>0.0723</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0284</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0403</v>
+        <v>0.0439</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2065</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1969</v>
+        <v>-2.2424</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7732</v>
+        <v>-2.8549</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5763</v>
+        <v>0.6125</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5108</v>
+        <v>-0.6645</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4234</v>
+        <v>1.2802</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9342</v>
+        <v>-1.9447</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4887</v>
+        <v>-1.3019</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2543</v>
+        <v>0.6558</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7655999999999999</v>
+        <v>-1.9577</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9994</v>
+        <v>0.6374</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8309</v>
+        <v>0.6244</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1685</v>
+        <v>0.013</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-1.1903</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4932</v>
+        <v>-0.4265</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5667</v>
+        <v>-0.3627</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0735</v>
+        <v>-0.0639</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4129</v>
+        <v>-2.3417</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6789</v>
+        <v>-2.3417</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5001</v>
+        <v>-2.503</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3651</v>
+        <v>-3.0793</v>
       </c>
       <c r="F11" t="n">
-        <v>0.865</v>
+        <v>0.5763</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6645</v>
+        <v>0.5108</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2802</v>
+        <v>-0.4234</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9447</v>
+        <v>0.9342</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3019</v>
+        <v>-0.4887</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6558</v>
+        <v>-1.2543</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9577</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6374</v>
+        <v>0.9994</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6244</v>
+        <v>0.8309</v>
       </c>
       <c r="O11" t="n">
-        <v>0.013</v>
+        <v>0.1685</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6842</v>
+        <v>-0.7992</v>
       </c>
       <c r="T11" t="n">
         <v>-0.8728</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1886</v>
+        <v>0.0735</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3417</v>
+        <v>-2.4129</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3417</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.639600000000001</v>
+        <v>3.9513</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.927300000000001</v>
+        <v>-9.6157</v>
       </c>
       <c r="F12" t="n">
-        <v>13.5672</v>
+        <v>13.5671</v>
       </c>
       <c r="G12" t="n">
         <v>8.072900000000001</v>
@@ -1360,16 +1360,16 @@
         <v>5.417199999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2.655799999999999</v>
+        <v>2.6558</v>
       </c>
       <c r="J12" t="n">
-        <v>3.921100000000001</v>
+        <v>3.9211</v>
       </c>
       <c r="K12" t="n">
         <v>3.5336</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3877000000000002</v>
+        <v>0.3877</v>
       </c>
       <c r="M12" t="n">
         <v>4.1517</v>
@@ -1390,13 +1390,13 @@
         <v>20.8304</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.401</v>
+        <v>-3.0892</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4282</v>
+        <v>-3.1165</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02709999999999996</v>
+        <v>0.02729999999999991</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0162</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7442</v>
+        <v>2.7592</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4827</v>
+        <v>-0.3449</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2615</v>
+        <v>3.1041</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1014</v>
+        <v>1.1157</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2672</v>
+        <v>-0.2668</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1658</v>
+        <v>1.3824</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3329</v>
+        <v>1.236</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2525</v>
+        <v>-0.0945</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0803</v>
+        <v>1.3304</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2314</v>
+        <v>-0.1203</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0147</v>
+        <v>-0.1723</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2461</v>
+        <v>0.052</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9919</v>
+        <v>-4.1661</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7935</v>
+        <v>3.7693</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2974</v>
+        <v>0.6391</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9353</v>
+        <v>-0.0225</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3621</v>
+        <v>0.6616</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5437</v>
+        <v>1.4012</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2065</v>
+        <v>2.6076</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3373</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2227</v>
+        <v>2.1407</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.549</v>
+        <v>0.8603</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7717</v>
+        <v>1.2804</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1157</v>
+        <v>-0.0573</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2668</v>
+        <v>0.615</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3824</v>
+        <v>-0.6723</v>
       </c>
       <c r="J14" t="n">
-        <v>1.236</v>
+        <v>1.276</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0945</v>
+        <v>1.1906</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3304</v>
+        <v>0.0854</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1203</v>
+        <v>-1.3333</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1723</v>
+        <v>-0.5755</v>
       </c>
       <c r="O14" t="n">
-        <v>0.052</v>
+        <v>-0.7577</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1661</v>
+        <v>-2.1822</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7693</v>
+        <v>3.1741</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1026</v>
+        <v>0.4081</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2265</v>
+        <v>-0.2379</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3292</v>
+        <v>0.646</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4012</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6076</v>
+        <v>2.0044</v>
       </c>
       <c r="X14" t="n">
         <v>-1.2065</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6941</v>
+        <v>2.0377</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3199</v>
+        <v>0.9726</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3742</v>
+        <v>1.0651</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7637</v>
+        <v>0.1014</v>
       </c>
       <c r="H15" t="n">
-        <v>0.923</v>
+        <v>0.2672</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1592</v>
+        <v>-0.1658</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7951</v>
+        <v>0.3329</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7148</v>
+        <v>0.2525</v>
       </c>
       <c r="L15" t="n">
         <v>0.0803</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0314</v>
+        <v>-0.2314</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2396</v>
+        <v>-0.2461</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.579</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.158</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2434</v>
+        <v>0.5909</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3411</v>
+        <v>0.4252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9023</v>
+        <v>0.1657</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>1.5437</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3417</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0757</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9442</v>
+        <v>1.3685</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2941</v>
+        <v>-1.0901</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2384</v>
+        <v>2.4586</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0415</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.403</v>
+        <v>0.0213</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0958</v>
+        <v>0.316</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9164</v>
+        <v>-0.0727</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3641</v>
+        <v>-0.4146</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2804</v>
+        <v>0.3419</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0573</v>
+        <v>0.7637</v>
       </c>
       <c r="H17" t="n">
-        <v>0.615</v>
+        <v>0.923</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6723</v>
+        <v>-0.1592</v>
       </c>
       <c r="J17" t="n">
-        <v>1.276</v>
+        <v>1.7951</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1906</v>
+        <v>1.7148</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0854</v>
+        <v>0.0803</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3333</v>
+        <v>-1.0314</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5755</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7577</v>
+        <v>-0.2396</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9919</v>
+        <v>-2.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1822</v>
+        <v>-5.158</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1741</v>
+        <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8162</v>
+        <v>1.4766</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4622</v>
+        <v>0.6066</v>
       </c>
       <c r="U17" t="n">
-        <v>0.646</v>
+        <v>0.87</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0044</v>
+        <v>2.3417</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0355</v>
+        <v>-0.7009</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8426</v>
+        <v>-0.9868</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8071</v>
+        <v>0.2859</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.2788</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3621</v>
+        <v>-1.2148</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9251</v>
+        <v>1.4936</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6264999999999999</v>
+        <v>0.3168</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2016</v>
+        <v>-0.6197</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8280999999999999</v>
+        <v>0.9365</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0634</v>
+        <v>-0.0379</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1605</v>
+        <v>-0.5951</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.097</v>
+        <v>0.5572</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6546</v>
+        <v>-0.17</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0339</v>
+        <v>-0.3117</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6885</v>
+        <v>0.1416</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0753</v>
+        <v>-1.0738</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.7406</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2704</v>
+        <v>1.6668</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8769</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.149</v>
+        <v>0.3621</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2721</v>
+        <v>-0.9251</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6802</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6802</v>
+        <v>0.2016</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1967</v>
+        <v>0.0634</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4688</v>
+        <v>0.1605</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2721</v>
+        <v>-0.097</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1984</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1247</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0737</v>
+        <v>0.5482</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1023</v>
+        <v>-1.0753</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0671</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0351</v>
+        <v>-0.2704</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3781</v>
+        <v>-0.8769</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7912</v>
+        <v>-1.149</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5869</v>
+        <v>0.2721</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2599</v>
+        <v>-0.6802</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.66</v>
+        <v>-0.6802</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1182</v>
+        <v>-0.1967</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1312</v>
+        <v>-0.4688</v>
       </c>
       <c r="O20" t="n">
-        <v>0.013</v>
+        <v>0.2721</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2126</v>
+        <v>-0.1984</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1928</v>
+        <v>-0.1247</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0198</v>
+        <v>-0.0737</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4491</v>
+        <v>-1.132</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.599</v>
+        <v>-1.3732</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1499</v>
+        <v>0.2412</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2788</v>
+        <v>-1.3781</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2148</v>
+        <v>-0.7912</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4936</v>
+        <v>-0.5869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3168</v>
+        <v>-1.2599</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6197</v>
+        <v>-0.66</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9365</v>
+        <v>-0.5999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0379</v>
+        <v>-0.1182</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5951</v>
+        <v>-0.1312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5572</v>
+        <v>0.013</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9182</v>
+        <v>0.1828</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9238</v>
+        <v>-0.1133</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0056</v>
+        <v>0.2961</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4236</v>
+        <v>-1.7731</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5821</v>
+        <v>-3.0719</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1585</v>
+        <v>1.2988</v>
       </c>
       <c r="G22" t="n">
         <v>-5.5054</v>
@@ -2170,13 +2170,13 @@
         <v>2.9758</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0142</v>
+        <v>0.6646</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5327</v>
+        <v>-0.0225</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6872</v>
       </c>
       <c r="V22" t="n">
         <v>2.0757</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0754</v>
+        <v>-5.4376</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2668</v>
+        <v>-4.5729</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8086</v>
+        <v>-0.8647</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9105</v>
@@ -2248,13 +2248,13 @@
         <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>0.212</v>
+        <v>-0.1502</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1503</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7979000000000001</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6396</v>
+        <v>-2.959299999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.5671</v>
+        <v>-13.567</v>
       </c>
       <c r="F24" t="n">
-        <v>9.9276</v>
+        <v>10.6077</v>
       </c>
       <c r="G24" t="n">
         <v>-8.0731</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.4172</v>
+        <v>-5.417199999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.655799999999999</v>
+        <v>-2.6558</v>
       </c>
       <c r="J24" t="n">
         <v>-4.1517</v>
@@ -2326,13 +2326,13 @@
         <v>18.8466</v>
       </c>
       <c r="S24" t="n">
-        <v>3.401</v>
+        <v>4.0812</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.02729999999999994</v>
+        <v>-0.02739999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4283</v>
+        <v>4.1084</v>
       </c>
       <c r="V24" t="n">
         <v>3.0161</v>
